--- a/valog_zinssaetze_data.xlsx
+++ b/valog_zinssaetze_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://valogit-my.sharepoint.com/personal/andreas_vasileiadis_valog_com/Documents/Desktop/python/DR/dummy fake/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_EF25F485F2DFA6A58A734653A2A1B43C8D1D3843" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{541660F0-1F26-4951-ABB5-4B21509E8818}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="11_EF25F485F2DFA6A58A734653A2A1B43C8D1D3843" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66752C15-011A-4E88-BB3A-85FD74EC4783}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1635" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1635" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UGB_Stichtagszins" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="37">
   <si>
     <t>date</t>
   </si>
@@ -121,6 +121,18 @@
   </si>
   <si>
     <t>2030-12-31</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>2023-03-31</t>
+  </si>
+  <si>
+    <t>2023-06-30</t>
+  </si>
+  <si>
+    <t>2023-09-30</t>
   </si>
 </sst>
 </file>
@@ -176,13 +188,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -485,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -852,6 +865,26 @@
         <v>0.01</v>
       </c>
     </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="C19" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -859,7 +892,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -895,7 +928,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3">
         <v>0.01</v>
@@ -921,85 +954,85 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.01</v>
+        <v>34</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.02</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.01</v>
+        <v>35</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.02</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.01</v>
+        <v>36</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.02</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="3">
         <v>0.01</v>
@@ -1025,7 +1058,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="3">
         <v>0.01</v>
@@ -1051,7 +1084,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="3">
         <v>0.01</v>
@@ -1077,7 +1110,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="3">
         <v>0.01</v>
@@ -1103,7 +1136,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="3">
         <v>0.01</v>
@@ -1129,7 +1162,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="3">
         <v>0.01</v>
@@ -1155,7 +1188,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3">
         <v>0.01</v>
@@ -1181,7 +1214,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="3">
         <v>0.01</v>
@@ -1207,7 +1240,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="3">
         <v>0.01</v>
@@ -1233,7 +1266,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="3">
         <v>0.01</v>
@@ -1259,7 +1292,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="3">
         <v>0.01</v>
@@ -1285,7 +1318,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" s="3">
         <v>0.01</v>
@@ -1311,7 +1344,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" s="3">
         <v>0.01</v>
@@ -1337,7 +1370,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B19" s="3">
         <v>0.01</v>
@@ -1363,7 +1396,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="3">
         <v>0.01</v>
@@ -1389,7 +1422,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="3">
         <v>0.01</v>
@@ -1415,7 +1448,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="3">
         <v>0.01</v>
@@ -1441,27 +1474,53 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="C23" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="D23" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="E23" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="F23" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="B24" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="H24" s="3">
         <v>0.01</v>
       </c>
     </row>
@@ -1472,7 +1531,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1501,7 +1560,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3">
         <v>0.01</v>
@@ -1521,7 +1580,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="3">
         <v>0.01</v>
@@ -1541,7 +1600,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="3">
         <v>0.01</v>
@@ -1561,7 +1620,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" s="3">
         <v>0.01</v>
@@ -1581,7 +1640,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="3">
         <v>0.01</v>
@@ -1601,7 +1660,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" s="3">
         <v>0.01</v>
@@ -1621,7 +1680,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" s="3">
         <v>0.01</v>
@@ -1641,7 +1700,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" s="3">
         <v>0.01</v>
@@ -1661,7 +1720,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3">
         <v>0.01</v>
@@ -1681,7 +1740,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B11" s="3">
         <v>0.01</v>
@@ -1701,7 +1760,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" s="3">
         <v>0.01</v>
@@ -1721,7 +1780,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13" s="3">
         <v>0.01</v>
@@ -1741,7 +1800,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B14" s="3">
         <v>0.01</v>
@@ -1761,7 +1820,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B15" s="3">
         <v>0.01</v>
@@ -1781,7 +1840,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B16" s="3">
         <v>0.01</v>
@@ -1801,42 +1860,22 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="C17" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="D17" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="C18" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="D18" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="E18" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0.01</v>
+        <v>33</v>
+      </c>
+      <c r="B17" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="C17" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>

--- a/valog_zinssaetze_data.xlsx
+++ b/valog_zinssaetze_data.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="UGB_Stichtagszins" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="UGB_Durchschnitt_15J" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="IFRS" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -466,792 +467,440 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023-03-31</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.88</v>
+        <v>0.39</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>0.58</v>
       </c>
       <c r="D2" t="n">
-        <v>3.81</v>
+        <v>0.77</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6</v>
+        <v>0.85</v>
       </c>
       <c r="F2" t="n">
-        <v>3.41</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023-04-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.88</v>
+        <v>0.86</v>
       </c>
       <c r="C3" t="n">
-        <v>3.82</v>
+        <v>1.15</v>
       </c>
       <c r="D3" t="n">
-        <v>3.84</v>
+        <v>1.34</v>
       </c>
       <c r="E3" t="n">
-        <v>3.69</v>
+        <v>1.39</v>
       </c>
       <c r="F3" t="n">
-        <v>3.49</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.86</v>
+        <v>4.08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.79</v>
+        <v>4.04</v>
       </c>
       <c r="D4" t="n">
-        <v>3.82</v>
+        <v>3.97</v>
       </c>
       <c r="E4" t="n">
-        <v>3.65</v>
+        <v>3.71</v>
       </c>
       <c r="F4" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.08</v>
+        <v>3.27</v>
       </c>
       <c r="C5" t="n">
-        <v>3.83</v>
+        <v>3.34</v>
       </c>
       <c r="D5" t="n">
-        <v>3.77</v>
+        <v>3.42</v>
       </c>
       <c r="E5" t="n">
-        <v>3.61</v>
+        <v>3.35</v>
       </c>
       <c r="F5" t="n">
-        <v>3.43</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2024-11-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.03</v>
+        <v>2.91</v>
       </c>
       <c r="C6" t="n">
-        <v>3.91</v>
+        <v>3.01</v>
       </c>
       <c r="D6" t="n">
-        <v>3.91</v>
+        <v>3.07</v>
       </c>
       <c r="E6" t="n">
-        <v>3.77</v>
+        <v>3.01</v>
       </c>
       <c r="F6" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.96</v>
+        <v>3.1</v>
       </c>
       <c r="C7" t="n">
-        <v>3.87</v>
+        <v>3.22</v>
       </c>
       <c r="D7" t="n">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="E7" t="n">
-        <v>3.77</v>
+        <v>3.21</v>
       </c>
       <c r="F7" t="n">
-        <v>3.61</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.24</v>
+        <v>3.15</v>
       </c>
       <c r="C8" t="n">
-        <v>4.23</v>
+        <v>3.26</v>
       </c>
       <c r="D8" t="n">
-        <v>4.28</v>
+        <v>3.33</v>
       </c>
       <c r="E8" t="n">
-        <v>4.16</v>
+        <v>3.27</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1</v>
+        <v>3.02</v>
       </c>
       <c r="C9" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="D9" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="E9" t="n">
-        <v>4.2</v>
+        <v>3.21</v>
       </c>
       <c r="F9" t="n">
-        <v>4.07</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023-11-30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.75</v>
+        <v>3.27</v>
       </c>
       <c r="C10" t="n">
-        <v>3.79</v>
+        <v>3.5</v>
       </c>
       <c r="D10" t="n">
-        <v>3.87</v>
+        <v>3.63</v>
       </c>
       <c r="E10" t="n">
-        <v>3.79</v>
+        <v>3.61</v>
       </c>
       <c r="F10" t="n">
-        <v>3.63</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.27</v>
+        <v>2.97</v>
       </c>
       <c r="C11" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="D11" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="E11" t="n">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="F11" t="n">
-        <v>3.24</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.35</v>
+        <v>3.04</v>
       </c>
       <c r="C12" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="D12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="F12" t="n">
         <v>3.5</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3.31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.63</v>
+        <v>3.12</v>
       </c>
       <c r="C13" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="D13" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="E13" t="n">
-        <v>3.48</v>
+        <v>3.68</v>
       </c>
       <c r="F13" t="n">
-        <v>3.35</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.51</v>
+        <v>3.22</v>
       </c>
       <c r="C14" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="D14" t="n">
-        <v>3.45</v>
+        <v>3.73</v>
       </c>
       <c r="E14" t="n">
-        <v>3.36</v>
+        <v>3.77</v>
       </c>
       <c r="F14" t="n">
-        <v>3.23</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.8</v>
+        <v>3.17</v>
       </c>
       <c r="C15" t="n">
-        <v>3.7</v>
+        <v>3.53</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="E15" t="n">
-        <v>3.59</v>
+        <v>3.83</v>
       </c>
       <c r="F15" t="n">
-        <v>3.44</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.85</v>
+        <v>3.23</v>
       </c>
       <c r="C16" t="n">
-        <v>3.74</v>
+        <v>3.55</v>
       </c>
       <c r="D16" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="E16" t="n">
-        <v>3.65</v>
+        <v>3.82</v>
       </c>
       <c r="F16" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.72</v>
+        <v>3.18</v>
       </c>
       <c r="C17" t="n">
-        <v>3.67</v>
+        <v>3.51</v>
       </c>
       <c r="D17" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="E17" t="n">
-        <v>3.61</v>
+        <v>3.81</v>
       </c>
       <c r="F17" t="n">
-        <v>3.46</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.41</v>
+        <v>3.27</v>
       </c>
       <c r="C18" t="n">
-        <v>3.41</v>
+        <v>3.64</v>
       </c>
       <c r="D18" t="n">
-        <v>3.5</v>
+        <v>3.89</v>
       </c>
       <c r="E18" t="n">
-        <v>3.42</v>
+        <v>3.99</v>
       </c>
       <c r="F18" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.34</v>
+        <v>3.43</v>
       </c>
       <c r="C19" t="n">
-        <v>3.39</v>
+        <v>3.82</v>
       </c>
       <c r="D19" t="n">
-        <v>3.47</v>
+        <v>4.07</v>
       </c>
       <c r="E19" t="n">
-        <v>3.41</v>
+        <v>4.17</v>
       </c>
       <c r="F19" t="n">
-        <v>3.29</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.06</v>
+        <v>3.37</v>
       </c>
       <c r="C20" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="D20" t="n">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>3.29</v>
+        <v>4.1</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="C21" t="n">
-        <v>3.27</v>
+        <v>3.54</v>
       </c>
       <c r="D21" t="n">
-        <v>3.32</v>
+        <v>3.78</v>
       </c>
       <c r="E21" t="n">
-        <v>3.23</v>
+        <v>3.89</v>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="C22" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="D22" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E22" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C23" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="D23" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="E23" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="F23" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="C24" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="D24" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="E24" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="F24" t="n">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="C25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="D25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="E25" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="F25" t="n">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="C26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D26" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="F26" t="n">
-        <v>3.51</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2025-04-30</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="C27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D27" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="E27" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="F27" t="n">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="C28" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="D28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="E28" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="F28" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="C29" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="D29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="E29" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="F29" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="C30" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="D30" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="E30" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="F30" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="C31" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="D31" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="E31" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="F31" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="C32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="D32" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="E32" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="F32" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="C33" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="D33" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="E33" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="F33" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="C34" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="D34" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="E34" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="F34" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="C35" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="D35" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="E35" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="F35" t="n">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="C36" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D36" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F36" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="C37" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="D37" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="E37" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="F37" t="n">
         <v>3.89</v>
       </c>
     </row>
@@ -1266,7 +915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1324,1009 +973,1223 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023-03-31</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.81</v>
+        <v>0.77</v>
       </c>
       <c r="C2" t="n">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="D2" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="E2" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="F2" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="G2" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="H2" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023-04-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.84</v>
+        <v>1.34</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="D3" t="n">
-        <v>1.84</v>
+        <v>1.46</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="F3" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="H3" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.82</v>
+        <v>3.97</v>
       </c>
       <c r="C4" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="D4" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="E4" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="F4" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="G4" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="H4" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.77</v>
+        <v>3.42</v>
       </c>
       <c r="C5" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="E5" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="F5" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="G5" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="H5" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2024-11-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.91</v>
+        <v>3.07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.89</v>
+        <v>2.43</v>
       </c>
       <c r="D6" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="E6" t="n">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="F6" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="H6" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="C7" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="D7" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="E7" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="F7" t="n">
-        <v>1.87</v>
+        <v>2.22</v>
       </c>
       <c r="G7" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="H7" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.28</v>
+        <v>3.33</v>
       </c>
       <c r="C8" t="n">
-        <v>1.95</v>
+        <v>2.51</v>
       </c>
       <c r="D8" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="E8" t="n">
-        <v>1.96</v>
+        <v>2.27</v>
       </c>
       <c r="F8" t="n">
-        <v>1.89</v>
+        <v>2.23</v>
       </c>
       <c r="G8" t="n">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="C9" t="n">
-        <v>1.99</v>
+        <v>2.55</v>
       </c>
       <c r="D9" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="E9" t="n">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="F9" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="G9" t="n">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="H9" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023-11-30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.87</v>
+        <v>3.63</v>
       </c>
       <c r="C10" t="n">
-        <v>2.02</v>
+        <v>2.59</v>
       </c>
       <c r="D10" t="n">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="E10" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="F10" t="n">
-        <v>1.94</v>
+        <v>2.27</v>
       </c>
       <c r="G10" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="H10" t="n">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="C11" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="D11" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="E11" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="F11" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="C12" t="n">
-        <v>2.07</v>
+        <v>2.68</v>
       </c>
       <c r="D12" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="E12" t="n">
-        <v>2.06</v>
+        <v>2.33</v>
       </c>
       <c r="F12" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95</v>
+        <v>2.22</v>
       </c>
       <c r="H12" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="C13" t="n">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="D13" t="n">
-        <v>2.09</v>
+        <v>2.44</v>
       </c>
       <c r="E13" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="G13" t="n">
-        <v>1.97</v>
+        <v>2.24</v>
       </c>
       <c r="H13" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.45</v>
+        <v>3.73</v>
       </c>
       <c r="C14" t="n">
-        <v>2.13</v>
+        <v>2.77</v>
       </c>
       <c r="D14" t="n">
-        <v>2.11</v>
+        <v>2.47</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="F14" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="G14" t="n">
-        <v>1.99</v>
+        <v>2.27</v>
       </c>
       <c r="H14" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="C15" t="n">
-        <v>2.17</v>
+        <v>2.82</v>
       </c>
       <c r="D15" t="n">
-        <v>2.13</v>
+        <v>2.51</v>
       </c>
       <c r="E15" t="n">
-        <v>2.12</v>
+        <v>2.39</v>
       </c>
       <c r="F15" t="n">
-        <v>2.05</v>
+        <v>2.36</v>
       </c>
       <c r="G15" t="n">
-        <v>2.01</v>
+        <v>2.29</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="C16" t="n">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="D16" t="n">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="E16" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="F16" t="n">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="G16" t="n">
-        <v>2.03</v>
+        <v>2.31</v>
       </c>
       <c r="H16" t="n">
-        <v>2.01</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="C17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H17" t="n">
         <v>2.24</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2.02</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.5</v>
+        <v>3.89</v>
       </c>
       <c r="C18" t="n">
-        <v>2.28</v>
+        <v>2.97</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="E18" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="F18" t="n">
-        <v>2.12</v>
+        <v>2.41</v>
       </c>
       <c r="G18" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="H18" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.47</v>
+        <v>4.07</v>
       </c>
       <c r="C19" t="n">
-        <v>2.33</v>
+        <v>3.03</v>
       </c>
       <c r="D19" t="n">
-        <v>2.22</v>
+        <v>2.66</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="F19" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="G19" t="n">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="H19" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>2.37</v>
+        <v>3.08</v>
       </c>
       <c r="D20" t="n">
-        <v>2.23</v>
+        <v>2.71</v>
       </c>
       <c r="E20" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="F20" t="n">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="G20" t="n">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="H20" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.32</v>
+        <v>3.78</v>
       </c>
       <c r="C21" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="D21" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="E21" t="n">
-        <v>2.23</v>
+        <v>2.53</v>
       </c>
       <c r="F21" t="n">
-        <v>2.19</v>
+        <v>2.47</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="H21" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024-11-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.07</v>
+        <v>3.78</v>
       </c>
       <c r="C22" t="n">
-        <v>2.43</v>
+        <v>3.55</v>
       </c>
       <c r="D22" t="n">
-        <v>2.26</v>
+        <v>3.16</v>
       </c>
       <c r="E22" t="n">
-        <v>2.24</v>
+        <v>2.83</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="G22" t="n">
-        <v>2.11</v>
+        <v>2.57</v>
       </c>
       <c r="H22" t="n">
-        <v>2.07</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.28</v>
+        <v>3.78</v>
       </c>
       <c r="C23" t="n">
-        <v>2.47</v>
+        <v>3.72</v>
       </c>
       <c r="D23" t="n">
-        <v>2.28</v>
+        <v>3.59</v>
       </c>
       <c r="E23" t="n">
-        <v>2.26</v>
+        <v>3.24</v>
       </c>
       <c r="F23" t="n">
-        <v>2.22</v>
+        <v>2.94</v>
       </c>
       <c r="G23" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="H23" t="n">
-        <v>2.08</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2028-12-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.33</v>
+        <v>3.78</v>
       </c>
       <c r="C24" t="n">
-        <v>2.51</v>
+        <v>3.7</v>
       </c>
       <c r="D24" t="n">
-        <v>2.3</v>
+        <v>3.73</v>
       </c>
       <c r="E24" t="n">
-        <v>2.27</v>
+        <v>3.62</v>
       </c>
       <c r="F24" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14</v>
+        <v>3.01</v>
       </c>
       <c r="H24" t="n">
-        <v>2.1</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2029-12-31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="C25" t="n">
-        <v>2.55</v>
+        <v>3.76</v>
       </c>
       <c r="D25" t="n">
-        <v>2.32</v>
+        <v>3.71</v>
       </c>
       <c r="E25" t="n">
-        <v>2.28</v>
+        <v>3.74</v>
       </c>
       <c r="F25" t="n">
-        <v>2.25</v>
+        <v>3.63</v>
       </c>
       <c r="G25" t="n">
-        <v>2.16</v>
+        <v>3.34</v>
       </c>
       <c r="H25" t="n">
-        <v>2.11</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2030-12-31</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="G26" t="n">
         <v>3.63</v>
       </c>
-      <c r="C26" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2.18</v>
-      </c>
       <c r="H26" t="n">
-        <v>2.13</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>2031-12-31</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020-12-31</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2021-12-31</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="C27" t="n">
+      <c r="B11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.23</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.37</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="C18" t="n">
         <v>2.63</v>
       </c>
-      <c r="D27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="C28" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="C29" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2.18</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="C30" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="D30" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="H30" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="C31" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="G31" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="H31" t="n">
-        <v>2.21</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="C32" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="D32" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E32" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="F32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="C33" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E33" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="F33" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="G33" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2.24</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
+      <c r="D18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D20" t="n">
         <v>3.89</v>
       </c>
-      <c r="C34" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="F34" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="H34" t="n">
-        <v>2.26</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="C35" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="D35" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="F35" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="H35" t="n">
-        <v>2.28</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>4</v>
-      </c>
-      <c r="C36" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F36" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H36" t="n">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="E20" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="C37" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="D37" t="n">
+      <c r="B21" t="n">
         <v>2.75</v>
       </c>
-      <c r="E37" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="F37" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="H37" t="n">
-        <v>2.32</v>
+      <c r="C21" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.64</v>
       </c>
     </row>
   </sheetData>

--- a/valog_zinssaetze_data.xlsx
+++ b/valog_zinssaetze_data.xlsx
@@ -890,7 +890,7 @@
         <v>2.16</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="3">
@@ -907,7 +907,7 @@
         <v>2.47</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>2.19</v>
@@ -916,7 +916,7 @@
         <v>2.14</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="4">
@@ -959,7 +959,7 @@
         <v>2.38</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>2.14</v>
@@ -994,7 +994,7 @@
         <v>2.08</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="7">
@@ -1020,7 +1020,7 @@
         <v>2.06</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="8">
@@ -1046,7 +1046,7 @@
         <v>2.04</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="9">
@@ -1063,7 +1063,7 @@
         <v>2.21</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>2.06</v>
@@ -1150,7 +1150,7 @@
         <v>1.95</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="13">
@@ -1228,7 +1228,7 @@
         <v>1.91</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="16">
@@ -1245,7 +1245,7 @@
         <v>1.99</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>1.94</v>
@@ -1271,7 +1271,7 @@
         <v>1.98</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>1.92</v>
@@ -1280,7 +1280,7 @@
         <v>1.89</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="18">
